--- a/datasets/tenant-inputs/templates/universal/standard-2026-07-v3/SA03_Vendor_Contracts_Extract_Template.xlsx
+++ b/datasets/tenant-inputs/templates/universal/standard-2026-07-v3/SA03_Vendor_Contracts_Extract_Template.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R8cf52219cdb74a94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="6" r:id="RabarvaStartHereGoverned"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet Guide" sheetId="1" r:id="R8cf52219cdb74a94"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Extract Intake" sheetId="2" r:id="R8a8232e185324d36"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Dimensions" sheetId="3" r:id="Rfc28c04be50b4ca9"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Questions" sheetId="4" r:id="R529aa0147c0f4f5a"/>
@@ -605,6 +606,251 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/abarvaStartHere.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="104" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SA03 Vendor Contracts Extract Template — Start Here</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This is a helper for a native system export. It shows the shape we can work with and where each exported field lands in the AbarVa model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">About this workbook</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What this workbook is</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A native source-extract helper. It is not a questionnaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Client-facing workstream(s)</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WS05 Vendors, Contracts, and Procurement</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who normally provides this</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">procurement; vendor management; legal; contract owners</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What usually populates it</t>
+        </is>
+      </c>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vendor master; CLM export; contract register; renewal calendar; sourcing history; rate cards where applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source extract templates that help</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SA03_Vendor_Contracts_Extract_Template.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canonical target file</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feeds several canonical files — see the Target Dimensions tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What to do</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 1</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open AbarVa_Template_Pack_Index_v3.xlsx first. Its Intake Workstreams and Review Queue sheets show the whole picture and who owns each part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 2</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Send us the raw export from the source system. Do not retype it into this workbook — the tabs here show the shape and the field mapping we expect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 3</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use the Sheet Guide tab for a description of every other tab in this workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 4</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review what we produce and tell us where it is wrong. Anything you cannot confirm should be left open as a gap rather than guessed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 5</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Record your review decision in the SME Review Matrix in AbarVa_Template_Pack_Index_v3.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before any of this is used</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closed gates</t>
+        </is>
+      </c>
+      <c r="B20" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This workbook is a template and review artifact. Completing it does not load data into any database, index retrieval, enable aVa or any product surface, or make its content client truth. SME validation and the promotion gates come first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What your SMEs confirm</t>
+        </is>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm vendor/contract ownership, supported systems/functions, renewal terms, risk, spend basis, and Source readiness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence we need with the data</t>
+        </is>
+      </c>
+      <c r="B22" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source system, report or export name, who owns it, when it was pulled, the period it covers, whether it is full or partial, and any known limitations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance reference</t>
+        </is>
+      </c>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/governance/CLIENT_REVIEW_WORKBOOK_QUALITY_BAR.md</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
